--- a/test_env/Comissoes_Recebimento_08_2025.xlsx
+++ b/test_env/Comissoes_Recebimento_08_2025.xlsx
@@ -554,12 +554,18 @@
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="n">
+        <v>0.01</v>
+      </c>
       <c r="H2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Adiantamento</t>
